--- a/duoki_editor/resources/data/blank/海洋-一般疑问句_否定答句认读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/海洋-一般疑问句_否定答句认读-1-blank.xlsx
@@ -88,16 +88,16 @@
     <t>叮咚！答对啦！宝石精灵在为你欢呼哟！再来一个更有趣的魔法问题，它是飞鱼吗？Is it a flying fish？</t>
   </si>
   <si>
+    <t>{sentence_answer_en_1}。</t>
+  </si>
+  <si>
     <t>{sentence_answer_en_2}。</t>
   </si>
   <si>
-    <t>{sentence_answer_en_1}。</t>
-  </si>
-  <si>
-    <t>这一题也答对啦！{user_name}，现在轮到你了！注意看屏幕，要根据屏幕上的提示来回答哦！它是飞鱼吗？Is it a flying fish？</t>
-  </si>
-  <si>
-    <t>哎呀，是调皮的风精灵偷走了你的声音吗？没关系，再大声说一遍吧！它是飞鱼吗？Is it a flying fish？</t>
+    <t>这一题也答对啦！{user_name}，现在轮到你了！注意看屏幕，要根据屏幕上的提示来回答哦！它是狗吗？Is it a dog？</t>
+  </si>
+  <si>
+    <t>哎呀，是调皮的风精灵偷走了你的声音吗？没关系，再大声说一遍吧！它是狗吗？Is it a dog？</t>
   </si>
   <si>
     <t>{sentence_answer_en_2}</t>
@@ -106,13 +106,13 @@
     <t>我来帮你吧！ {sentence_answer_en_2}</t>
   </si>
   <si>
-    <t>恭喜挑战成功！你们赢得了20颗宝石！</t>
-  </si>
-  <si>
-    <t>这次{npc2_name}帮了你，只能得到10颗宝石哦！下次要继续加油！</t>
-  </si>
-  <si>
-    <t>20|10</t>
+    <t>恭喜挑战成功！你们赢得了10颗宝石！</t>
+  </si>
+  <si>
+    <t>这次{npc2_name}帮了你，只能得到5颗宝石哦！下次要继续加油！</t>
+  </si>
+  <si>
+    <t>10|5</t>
   </si>
 </sst>
 </file>
